--- a/data/trans_orig/Q57-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Provincia-trans_orig.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la autopercepción de felicidad</t>
+          <t>Puntuación media de la autopercepción de felicidad (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,65</t>
+          <t>7,16; 7,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,45</t>
+          <t>6,95; 7,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 7,93</t>
+          <t>7,77; 7,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,49</t>
+          <t>7,15; 7,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 8,01</t>
+          <t>7,77; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 7,97</t>
+          <t>7,72; 7,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,66; 8,91</t>
+          <t>8,67; 8,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 7,95</t>
+          <t>7,78; 7,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 8,98</t>
+          <t>8,79; 8,98</t>
         </is>
       </c>
     </row>
@@ -796,27 +796,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 8,22</t>
+          <t>7,8; 8,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 7,88</t>
+          <t>7,59; 7,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 7,96</t>
+          <t>7,64; 7,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 7,94</t>
+          <t>7,78; 7,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 8,04</t>
+          <t>7,77; 8,03</t>
         </is>
       </c>
     </row>
@@ -871,32 +871,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 8,08</t>
+          <t>7,73; 8,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 8,23</t>
+          <t>7,83; 8,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,68</t>
+          <t>7,23; 7,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 8,11</t>
+          <t>7,84; 8,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,83</t>
+          <t>7,53; 7,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 8,12</t>
+          <t>7,91; 8,13</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,22</t>
+          <t>6,74; 7,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 8,34</t>
+          <t>8,06; 8,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 6,94</t>
+          <t>6,55; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,01; 8,26</t>
+          <t>8,01; 8,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,01</t>
+          <t>6,7; 7,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 8,25</t>
+          <t>8,08; 8,26</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1031,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,23</t>
+          <t>7,8; 8,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,75; 8,19</t>
+          <t>7,73; 8,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,93</t>
+          <t>7,41; 7,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,12</t>
+          <t>7,68; 8,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,03</t>
+          <t>7,68; 8,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 8,1</t>
+          <t>7,8; 8,1</t>
         </is>
       </c>
     </row>
@@ -1111,32 +1111,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 7,85</t>
+          <t>7,63; 7,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 8,34</t>
+          <t>8,03; 8,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,67</t>
+          <t>7,41; 7,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,03</t>
+          <t>7,39; 8,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,72</t>
+          <t>7,55; 7,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,12</t>
+          <t>7,58; 8,13</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,54</t>
+          <t>7,35; 7,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,64; 8,57</t>
+          <t>7,63; 8,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,3</t>
+          <t>7,07; 7,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,29</t>
+          <t>7,01; 7,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,15</t>
+          <t>7,38; 8,19</t>
         </is>
       </c>
     </row>
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,74</t>
+          <t>7,64; 7,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,38</t>
+          <t>8,13; 8,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,38; 7,5</t>
+          <t>7,39; 7,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,13</t>
+          <t>7,94; 8,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q57-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Provincia-trans_orig.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>7,98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,66</t>
+          <t>7,17; 7,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 8,12</t>
+          <t>7,87; 8,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,45</t>
+          <t>6,95; 7,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,77; 7,94</t>
+          <t>7,81; 7,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 8,01</t>
+          <t>7,86; 8,0</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>8,9</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 9,13</t>
+          <t>8,82; 9,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 7,96</t>
+          <t>7,7; 7,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 8,9</t>
+          <t>8,7; 8,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 7,96</t>
+          <t>7,78; 7,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 8,98</t>
+          <t>8,8; 8,99</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>7,98</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,8</t>
+          <t>7,81</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>7,89</t>
         </is>
       </c>
     </row>
@@ -791,32 +791,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 8,1</t>
+          <t>7,88; 8,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 8,24</t>
+          <t>7,74; 8,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 7,87</t>
+          <t>7,6; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,96</t>
+          <t>7,66; 7,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 7,95</t>
+          <t>7,77; 7,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 8,03</t>
+          <t>7,75; 8,02</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>8,07</t>
         </is>
       </c>
     </row>
@@ -871,32 +871,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,1</t>
+          <t>7,71; 8,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,21</t>
+          <t>7,91; 8,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,65</t>
+          <t>7,24; 7,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 8,11</t>
+          <t>7,85; 8,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,82</t>
+          <t>7,52; 7,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 8,13</t>
+          <t>7,95; 8,18</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>8,22</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>8,17</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,22</t>
+          <t>6,74; 7,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 8,34</t>
+          <t>8,08; 8,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,01; 8,25</t>
+          <t>8,01; 8,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,01</t>
+          <t>6,7; 7,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>7,9</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1031,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 8,22</t>
+          <t>7,82; 8,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,18</t>
+          <t>7,67; 8,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,93</t>
+          <t>7,42; 7,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,08</t>
+          <t>7,69; 8,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,0</t>
+          <t>7,68; 8,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 8,1</t>
+          <t>7,75; 8,04</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>8,08</t>
         </is>
       </c>
     </row>
@@ -1111,32 +1111,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,86</t>
+          <t>7,62; 7,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 8,34</t>
+          <t>8,05; 8,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,68</t>
+          <t>7,42; 7,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,03</t>
+          <t>7,88; 8,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 7,73</t>
+          <t>7,56; 7,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,58; 8,13</t>
+          <t>7,99; 8,17</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>7,42</t>
         </is>
       </c>
     </row>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,63; 8,58</t>
+          <t>7,56; 7,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,29</t>
+          <t>7,07; 7,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,28</t>
+          <t>7,01; 7,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,19</t>
+          <t>7,32; 7,51</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>8,02</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,74</t>
+          <t>7,63; 7,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,13; 8,39</t>
+          <t>8,07; 8,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 7,93</t>
+          <t>7,85; 7,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,61</t>
+          <t>7,52; 7,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,94; 8,13</t>
+          <t>7,97; 8,05</t>
         </is>
       </c>
     </row>
